--- a/analysis/myclass-chatbot/data/2026-06_챗봇분석_데이터통합.xlsx
+++ b/analysis/myclass-chatbot/data/2026-06_챗봇분석_데이터통합.xlsx
@@ -8,22 +8,22 @@
   </bookViews>
   <sheets>
     <sheet name="목차" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="대분류" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="중분류" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="상담대상" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="접수형태" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="학년" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="처리상태" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="일별추세" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="요일패턴" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="의도분류" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="성공률_분모별" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="성공률_분류(95)" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="조회baseline" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="MoM(5-6월)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="카_카테고리" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="카_발신비율" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="카_성공률분류" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="AMS_대분류" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="AMS_중분류" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="AMS_상담대상" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="AMS_접수형태" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="AMS_학년" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="AMS_처리상태" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="AMS_일별추세" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="AMS_요일패턴" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="AMS_의도분류" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="AMS_성공률_분모별" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="AMS_성공률_분류" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="AMS_조회baseline" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="AMS_MoM_5_6월" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="카카오_카테고리" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="카카오_발신비율" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="카카오_성공률분류" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,13 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,7 +60,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="0018181B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008A5A00"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,10 +86,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -442,272 +468,376 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>시트</t>
+          <t>출처</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>시트(탭)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>행수</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>대분류</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>AMS 6월 대분류 12종 빈도</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>13</v>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>■ AMS — 상담실장 기록 (전화상담, 81,863건)</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>중분류</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AMS 6월 중분류 95종</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>95</v>
+          <t>AMS_대분류</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>대분류 12종 빈도</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>상담대상</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>학부모/학생</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
+          <t>AMS_중분류</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>중분류 95종</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>접수형태</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>전화/방문/문자</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>3</v>
+          <t>AMS_상담대상</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>학부모/학생</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>학년</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>학년 분포</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>13</v>
+          <t>AMS_접수형태</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>전화/방문/문자</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>처리상태</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>처리완료 100%</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
+          <t>AMS_학년</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>학년 분포</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>일별추세</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6/1~30 일별</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>30</v>
+          <t>AMS_처리상태</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>처리완료 100%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>요일패턴</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>요일별(주말 피크)</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>7</v>
+          <t>AMS_일별추세</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6/1~30 일별</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>의도분류</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>조회/처리/컨설팅/혼합</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>4</v>
+          <t>AMS_요일패턴</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>요일별(주말 피크)</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>성공률_분모별</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>전체/비컨설팅/조회전용</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>3</v>
+          <t>AMS_의도분류</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>조회/처리/컨설팅/혼합</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>성공률_분류(95)</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>중분류별 챗봇 해결률</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>95</v>
+          <t>AMS_성공률_분모별</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>전체/비컨설팅/조회전용</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>조회baseline</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M1 Before 고정</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>17</v>
+          <t>AMS_성공률_분류</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>중분류별 해결률(95)</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MoM(5-6월)</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>전월 대비</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>14</v>
+          <t>AMS_조회baseline</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>M1 Before 고정</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>카_카테고리</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>카카오 12카테고리</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>카_발신비율</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>시스템/고객/상담원</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>3</v>
+          <t>AMS_MoM_5_6월</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>전월 대비</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>■ 카카오 — 채팅 채널 (162 대화 / 1,468 메시지)</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>카_성공률분류</t>
+          <t>카카오</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>카카오 해결률</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
+          <t>카카오_카테고리</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>12 카테고리</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>12</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>카카오</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>카카오_발신비율</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>시스템/고객/상담원</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>카카오</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>카카오_성공률분류</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>카테고리별 해결률</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -715,6 +845,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E78"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -727,17 +858,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>의도유형</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>건수</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>비중%</t>
         </is>
@@ -803,6 +934,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E78"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -818,32 +950,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>분모</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>건수</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>현재해결률_보수%</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>현재해결률_낙관%</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>2차후_보수%</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>2차후_낙관%</t>
         </is>
@@ -915,6 +1047,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E78"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -932,42 +1065,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>대분류/중분류</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>6월건수</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>의도유형</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>현재해결률_보수%</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>현재해결률_낙관%</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>2차후_보수%</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>2차후_낙관%</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>판정근거</t>
         </is>
@@ -4021,6 +4154,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E78"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -4033,17 +4167,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>중분류</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>6월건수</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>현재해결률_보수%</t>
         </is>
@@ -4278,6 +4412,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E78"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -4291,22 +4426,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>대분류</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>5월(건)</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>6월(건)</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>증감%</t>
         </is>
@@ -4544,6 +4679,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="008A5A00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -4556,17 +4692,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>카테고리</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>대화수</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>비중%</t>
         </is>
@@ -4736,6 +4872,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="008A5A00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -4748,17 +4885,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>발신자</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>메시지수</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>비중%</t>
         </is>
@@ -4811,6 +4948,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="008A5A00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -4825,27 +4963,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>카테고리</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>대화수</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>유형</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>현재해결률%</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>2차후%</t>
         </is>
@@ -5111,6 +5249,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E78"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -5123,17 +5262,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>대분류</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>건수</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>비중%</t>
         </is>
@@ -5316,6 +5455,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E78"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -5329,22 +5469,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>대분류</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>중분류</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>건수</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>비중%</t>
         </is>
@@ -7068,6 +7208,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E78"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -7080,17 +7221,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>상담대상</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>건수</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>비중%</t>
         </is>
@@ -7130,6 +7271,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E78"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -7142,17 +7284,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>접수형태</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>건수</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>비중%</t>
         </is>
@@ -7205,6 +7347,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E78"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -7217,17 +7360,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>학년</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>건수</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>비중%</t>
         </is>
@@ -7410,6 +7553,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E78"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -7422,17 +7566,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>처리상태</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>건수</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>비중%</t>
         </is>
@@ -7459,6 +7603,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E78"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -7470,12 +7615,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>날짜</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>건수</t>
         </is>
@@ -7789,6 +7934,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E78"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -7800,12 +7946,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>요일</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>건수</t>
         </is>
